--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -3602,25 +3602,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>16</v>
@@ -3667,25 +3667,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="F59" s="3">
-        <v>8800</v>
+        <v>9200</v>
       </c>
       <c r="G59" s="3">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="H59" s="3">
-        <v>9600</v>
+        <v>9900</v>
       </c>
       <c r="I59" s="3">
-        <v>20000</v>
+        <v>20400</v>
       </c>
       <c r="J59" s="3">
-        <v>14900</v>
+        <v>15300</v>
       </c>
       <c r="K59" s="3">
         <v>4800</v>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,301 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G8" s="3">
         <v>14700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>15000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>12100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>10000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>11100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>10400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>7500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>1300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>2200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>2900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8200</v>
+        <v>7200</v>
       </c>
       <c r="E9" s="3">
-        <v>8400</v>
+        <v>7400</v>
       </c>
       <c r="F9" s="3">
-        <v>4400</v>
+        <v>6800</v>
       </c>
       <c r="G9" s="3">
         <v>8200</v>
       </c>
       <c r="H9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K9" s="3">
         <v>7500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>9400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>7200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1400</v>
-      </c>
-      <c r="T9" s="3">
-        <v>2300</v>
       </c>
       <c r="U9" s="3">
         <v>1300</v>
       </c>
       <c r="V9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="X9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>6600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>7700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>3600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>300</v>
       </c>
       <c r="N10" s="3">
+        <v>300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +1012,85 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G12" s="3">
         <v>16400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="H12" s="3">
         <v>19300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="I12" s="3">
         <v>21000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
         <v>18500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
         <v>18400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>17900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <v>15100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>13700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="O12" s="3">
         <v>9100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="R12" s="3">
         <v>2600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="S12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="T12" s="3">
         <v>1700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="V12" s="3">
         <v>2100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <v>4500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Y12" s="3">
         <v>1800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,41 +1154,50 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
         <v>40500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>140300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1148,14 +1207,14 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1169,8 +1228,17 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1302,17 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1333,159 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F17" s="3">
+        <v>48100</v>
+      </c>
+      <c r="G17" s="3">
         <v>45200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>46200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>84800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>43800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>43200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>43300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>176800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>25800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>20700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>10400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>10500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>20300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>5100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>5500</v>
-      </c>
-      <c r="T17" s="3">
-        <v>11300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>6600</v>
       </c>
       <c r="V17" s="3">
         <v>5500</v>
       </c>
       <c r="W17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="X17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Z17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-30500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>-31200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-72700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-33800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>-32100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-32900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-169300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-24500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-19900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-8500</v>
       </c>
       <c r="O18" s="3">
         <v>-19900</v>
       </c>
       <c r="P18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="S18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>-3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>-8400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>-4900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,103 +1509,115 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G20" s="3">
         <v>21100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>53200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
         <v>-14200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
         <v>-33300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
         <v>-8200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>-8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="G21" s="3">
         <v>-7800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>23500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>-85700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>-63900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="K21" s="3">
         <v>-38600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>-32600</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1541,8 +1651,17 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,112 +1725,130 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-67100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-9300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>22000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-86900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-67100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-40300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-33700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-163900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-18800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-13800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-9300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-17400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>-20700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-4300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>-4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>-4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>16</v>
       </c>
@@ -1721,14 +1858,14 @@
       <c r="R24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1736,8 +1873,17 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1947,165 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="G26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>22000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-87900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-67100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-40000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-33300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-159700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-18300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-13600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-17400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>-20700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>-4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-9100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>22200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>-87700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>-66900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>-39700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-33100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-159600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>-18200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>-13600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>-17400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>-20700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-2700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>-1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2169,17 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2243,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2317,17 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2391,165 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>31200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-21100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>-53200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="I32" s="3">
         <v>14200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
         <v>33300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
         <v>8200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>-5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>-5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>-6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="S32" s="3">
         <v>4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>-5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>-3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="G33" s="3">
         <v>-9100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>22200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-87700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-66900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-39700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-33100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-159600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-18200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-13600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>-17400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>-20700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>-2700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>-1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2613,170 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="G35" s="3">
         <v>-9100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>22200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-87700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-66900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-39700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-33100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-159600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-18200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-13600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>-17400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>-20700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>-2700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>-1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2800,11 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2828,85 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>793000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>851500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>872700</v>
+      </c>
+      <c r="G41" s="3">
         <v>954400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>986000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>1032000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>1020300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>1217300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>1248000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>1291200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>1385400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>1321800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>1395900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>670900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>37300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>39700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>4500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>3900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>5500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>5300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>10200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>3800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2653,18 +2922,18 @@
       <c r="G42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" s="3">
         <v>20600</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2674,14 +2943,14 @@
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2701,138 +2970,165 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G43" s="3">
         <v>17900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>16200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>12800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>8900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>12500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>13500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>9300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>4700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>1200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>2100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>2400</v>
-      </c>
-      <c r="S43" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1700</v>
       </c>
       <c r="U43" s="3">
         <v>2400</v>
       </c>
       <c r="V43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y43" s="3">
         <v>1900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>21300</v>
+      </c>
+      <c r="G44" s="3">
         <v>19500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>20000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>19400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>17800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>16000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>15100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>11200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>4000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>4100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>3200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>3300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>4000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>4000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>3700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>3500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>3600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>4000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>3300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>3100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2858,32 +3154,32 @@
         <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
+        <v>100</v>
+      </c>
+      <c r="S45" s="3">
         <v>9900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
@@ -2894,123 +3190,141 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>831000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>894000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>909200</v>
+      </c>
+      <c r="G46" s="3">
         <v>991900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>1022300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>1064300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>1047100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>1266400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>1276700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>1311900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>1394300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>1330300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>1401100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>676100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>42600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>54500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>10300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>9900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>11900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>11000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>15900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>8800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>138400</v>
+      </c>
+      <c r="F47" s="3">
+        <v>132800</v>
+      </c>
+      <c r="G47" s="3">
         <v>173000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>161100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>115800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>168100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>28700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>63100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>64400</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>75100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>75100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R47" s="3">
         <v>8400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3020,144 +3334,171 @@
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>27800</v>
+      </c>
+      <c r="G48" s="3">
         <v>28100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>25500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>22400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>27100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>25000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>12200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>12400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>12000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>9500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>7200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>6600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>7100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>9000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>7000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>7300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>5200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>16</v>
+        <v>2200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2200</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="3">
         <v>31800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>20400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>21400</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N49" s="3">
         <v>116800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>118200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>4200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>4400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>4600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>4800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="T49" s="3">
         <v>5000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="U49" s="3">
         <v>5200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="V49" s="3">
         <v>5400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="W49" s="3">
         <v>5600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="X49" s="3">
         <v>5800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Y49" s="3">
         <v>6000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Z49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3562,17 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,46 +3636,55 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
@@ -3343,16 +3702,25 @@
         <v>400</v>
       </c>
       <c r="U52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3784,91 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>974000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1064300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1073100</v>
+      </c>
+      <c r="G54" s="3">
         <v>1194200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>1210200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>1203500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>1275900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>1342400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>1387700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>1390000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>1523900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>1536200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>1490400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>689300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>63300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>66400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>22800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>22900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>26700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>24000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>29300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>20300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3892,11 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,105 +3920,117 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>34400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>36800</v>
+      </c>
+      <c r="G57" s="3">
         <v>29000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>28700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>27900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>21800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>24600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>23100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>16700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>9800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>8500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>6700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>3900</v>
-      </c>
-      <c r="T57" s="3">
-        <v>4000</v>
       </c>
       <c r="U57" s="3">
         <v>4400</v>
       </c>
       <c r="V57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="W57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Y57" s="3">
         <v>3600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Z57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>16</v>
+        <v>400</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>16</v>
@@ -3640,14 +4041,14 @@
       <c r="P58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3661,47 +4062,56 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>8600</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K59" s="3">
         <v>9900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>20400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>15300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>4800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>6300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3711,14 +4121,14 @@
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -3726,203 +4136,239 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>29300</v>
+        <v>30400</v>
       </c>
       <c r="E60" s="3">
-        <v>34100</v>
+        <v>34500</v>
       </c>
       <c r="F60" s="3">
         <v>37000</v>
       </c>
       <c r="G60" s="3">
+        <v>29300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J60" s="3">
         <v>30300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>34500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>43500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>32000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>14500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>14800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>7100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>6700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
-      </c>
-      <c r="R60" s="3">
-        <v>4400</v>
-      </c>
-      <c r="S60" s="3">
-        <v>3900</v>
-      </c>
-      <c r="T60" s="3">
-        <v>4000</v>
       </c>
       <c r="U60" s="3">
         <v>4400</v>
       </c>
       <c r="V60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="W60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>3600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G61" s="3">
         <v>10800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>12100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>13100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>11300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>11900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>14200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>4400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>3600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>3900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>3300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>2600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>1800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="S61" s="3">
         <v>1700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>1800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>2100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="V61" s="3">
         <v>3500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="W61" s="3">
         <v>1300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="X61" s="3">
         <v>1400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G62" s="3">
         <v>4500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>8600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>14800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>10300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>12800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>3500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>1400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="U62" s="3">
         <v>4700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="V62" s="3">
         <v>8400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="W62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>7400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>1100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4432,17 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4506,17 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4580,91 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>49600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>51600</v>
+      </c>
+      <c r="G66" s="3">
         <v>45500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>50300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>53900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>45200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>51000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>67200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>46600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>29300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>33400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>20700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>22100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>10600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>8800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>7400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>11300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>15800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>8900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>13200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>4700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4688,11 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4756,17 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4830,17 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4904,17 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4978,91 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-626000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-591200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-590200</v>
+      </c>
+      <c r="G72" s="3">
         <v>-523600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-514400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>-536700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-449000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-382100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-342300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-309200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-149600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-131400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-117800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-108500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-91000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-70300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-62000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-60000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-58600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>-54300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>-53100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-51600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +5126,17 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5200,17 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +5274,91 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>928400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1014800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1021500</v>
+      </c>
+      <c r="G76" s="3">
         <v>1148700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>1159900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>1149500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>1230700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>1291400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>1320500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>1343400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>1494700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>1502700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>1469700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>667100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>52700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>57600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>15300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>11600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>10900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>15100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>16100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>15600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5422,170 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="G81" s="3">
         <v>-9100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>22200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-87700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-66900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-39700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-33100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-159600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-18200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-13600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>-17400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>-20700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>-2700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>-1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,38 +5609,41 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5057,14 +5653,14 @@
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5081,8 +5677,17 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5751,17 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5825,17 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5899,17 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5973,17 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,38 +6047,47 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="G89" s="3">
         <v>-28200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-28000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-26400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-22300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-21900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-21400</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5447,14 +6097,14 @@
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -5471,8 +6121,17 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,55 +6155,58 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5561,8 +6223,17 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6297,17 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,38 +6371,47 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-139500</v>
+      </c>
+      <c r="F94" s="3">
+        <v>122700</v>
+      </c>
+      <c r="G94" s="3">
         <v>75600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>-225400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>340700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-313800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-53400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-41200</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5732,14 +6421,14 @@
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -5756,8 +6445,17 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6479,11 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6547,17 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6621,17 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6695,17 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,38 +6769,47 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="G100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>-19800</v>
       </c>
-      <c r="F100" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6082,14 +6819,14 @@
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -6106,38 +6843,47 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6147,14 +6893,14 @@
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -6171,38 +6917,47 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-179800</v>
+      </c>
+      <c r="F102" s="3">
+        <v>34800</v>
+      </c>
+      <c r="G102" s="3">
         <v>42400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-273200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>315200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-336000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-81900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-65500</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6212,14 +6967,14 @@
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
@@ -6234,6 +6989,15 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,182 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>800</v>
       </c>
       <c r="P8" s="3">
         <v>800</v>
       </c>
       <c r="Q8" s="3">
+        <v>800</v>
+      </c>
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2900</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1700</v>
       </c>
       <c r="Y8" s="3">
         <v>1700</v>
@@ -839,156 +843,165 @@
       <c r="Z8" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="N9" s="3">
         <v>7200</v>
       </c>
-      <c r="E9" s="3">
-        <v>7400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>8400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>8200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>7500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>9400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6200</v>
+        <v>6800</v>
       </c>
       <c r="E10" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F10" s="3">
         <v>7100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>300</v>
       </c>
       <c r="N10" s="3">
         <v>300</v>
       </c>
       <c r="O10" s="3">
+        <v>300</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1100</v>
-      </c>
-      <c r="R10" s="3">
-        <v>-100</v>
       </c>
       <c r="S10" s="3">
         <v>-100</v>
       </c>
       <c r="T10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1024,73 +1038,76 @@
         <v>9100</v>
       </c>
       <c r="E12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F12" s="3">
         <v>13600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3700</v>
       </c>
       <c r="Q12" s="3">
         <v>3700</v>
       </c>
       <c r="R12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,13 +1180,16 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1180,27 +1200,27 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>40500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>140300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1216,8 +1236,8 @@
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E17" s="3">
         <v>32300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>84800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>176800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-72700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-169300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,115 +1545,119 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>26100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>21100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>53200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-33300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-65600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>23500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-85700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-63900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-38600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-32600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1660,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,124 +1774,130 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-67100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-86900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-67100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-40300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-163900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>16</v>
       </c>
@@ -1867,8 +1913,8 @@
       <c r="U24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-66900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-87900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-67100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-40000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-159700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-66600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-87700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-66900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-39700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-159600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E32" s="3">
         <v>16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-26100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-21100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-53200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>33300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-66600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-87700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-66900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-39700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-159600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-66600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-87700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-66900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-39700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-159600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,112 +2917,116 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>763800</v>
+      </c>
+      <c r="E41" s="3">
         <v>793000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>851500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>872700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>954400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>986000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1032000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1020300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1217300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1248000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1291200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1385400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1321800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1395900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>670900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>37300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="3">
         <v>20600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2952,8 +3042,8 @@
       <c r="Q42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2979,156 +3069,165 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E43" s="3">
         <v>18300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E44" s="3">
         <v>19700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3300</v>
-      </c>
-      <c r="R44" s="3">
-        <v>4000</v>
       </c>
       <c r="S44" s="3">
         <v>4000</v>
       </c>
       <c r="T44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U44" s="3">
         <v>3700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3163,13 +3262,13 @@
         <v>100</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3178,11 +3277,11 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
         <v>9900</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
@@ -3199,135 +3298,141 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>800500</v>
+      </c>
+      <c r="E46" s="3">
         <v>831000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>894000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>909200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>991900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1022300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1064300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1047100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1266400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1276700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1311900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1394300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1330300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1401100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>676100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E47" s="3">
         <v>112700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>138400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>132800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>173000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>161100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>115800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>168100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>63100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64400</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
-        <v>75100</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>75100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>75100</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S47" s="3">
         <v>8400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3343,88 +3448,94 @@
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E48" s="3">
         <v>27200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>5200</v>
       </c>
       <c r="Z48" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3438,67 +3549,70 @@
         <v>2200</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" s="3">
         <v>31800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O49" s="3">
         <v>116800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>118200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3657,37 +3777,37 @@
         <v>900</v>
       </c>
       <c r="F52" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G52" s="3">
         <v>1100</v>
       </c>
       <c r="H52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
       </c>
       <c r="N52" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>500</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
@@ -3711,16 +3831,19 @@
         <v>400</v>
       </c>
       <c r="X52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y52" s="3">
         <v>300</v>
       </c>
       <c r="Z52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E54" s="3">
         <v>974000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1064300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1073100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1194200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1210200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1203500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1275900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1342400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1387700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1390000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1523900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1536200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1490400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>689300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>63300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,108 +4053,112 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E57" s="3">
         <v>26000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>4500</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>300</v>
       </c>
       <c r="H58" s="3">
         <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3">
         <v>400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4032,8 +4166,8 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>16</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>16</v>
@@ -4050,8 +4184,8 @@
       <c r="S58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4071,13 +4205,16 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -4089,32 +4226,32 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4130,8 +4267,8 @@
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4145,230 +4282,242 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E60" s="3">
         <v>30400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7400</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>1100</v>
       </c>
       <c r="Z62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E66" s="3">
         <v>45600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-670000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-626000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-591200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-590200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-523600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-514400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-536700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-449000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-382100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-342300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-309200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-149600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-131400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-117800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-108500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-91000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-70300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-62000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-60000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-58600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-54300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-51600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>869600</v>
+      </c>
+      <c r="E76" s="3">
         <v>928400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1014800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1021500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1148700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1159900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1149500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1230700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1291400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1320500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1343400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1494700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1502700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1469700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>667100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>57600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-66600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-87700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-66900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-39700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-159600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,41 +5810,42 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5662,8 +5861,8 @@
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,41 +6270,44 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-29400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6106,8 +6323,8 @@
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,38 +6378,39 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -6199,8 +6420,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
@@ -6208,8 +6429,8 @@
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,41 +6607,44 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E94" s="3">
         <v>9100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-139500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>122700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>75600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-225400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>340700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-313800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-53400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41200</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6430,8 +6660,8 @@
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,41 +7021,44 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-53200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-67300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-19800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6828,8 +7074,8 @@
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -6852,41 +7098,44 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-1100</v>
       </c>
       <c r="G101" s="3">
         <v>-1100</v>
       </c>
       <c r="H101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6902,8 +7151,8 @@
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6926,41 +7175,44 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-57700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-179800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>42400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-273200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>315200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-336000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-81900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6976,8 +7228,8 @@
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -6998,6 +7250,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,189 +656,193 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1300</v>
-      </c>
-      <c r="P8" s="3">
-        <v>800</v>
       </c>
       <c r="Q8" s="3">
         <v>800</v>
       </c>
       <c r="R8" s="3">
+        <v>800</v>
+      </c>
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1700</v>
       </c>
       <c r="Z8" s="3">
         <v>1700</v>
@@ -846,162 +850,171 @@
       <c r="AA8" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E9" s="3">
         <v>8200</v>
       </c>
-      <c r="E9" s="3">
-        <v>7100</v>
-      </c>
       <c r="F9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G9" s="3">
         <v>7400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="3">
         <v>6800</v>
       </c>
-      <c r="E10" s="3">
-        <v>6300</v>
-      </c>
       <c r="F10" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G10" s="3">
         <v>7100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>300</v>
       </c>
       <c r="O10" s="3">
         <v>300</v>
       </c>
       <c r="P10" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
-      </c>
-      <c r="S10" s="3">
-        <v>-100</v>
       </c>
       <c r="T10" s="3">
         <v>-100</v>
       </c>
       <c r="U10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>9100</v>
+        <v>9800</v>
       </c>
       <c r="E12" s="3">
         <v>9100</v>
       </c>
       <c r="F12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G12" s="3">
         <v>13600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>3700</v>
       </c>
       <c r="R12" s="3">
         <v>3700</v>
       </c>
       <c r="S12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T12" s="3">
         <v>2600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,47 +1200,50 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
         <v>40500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3">
         <v>140300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1239,8 +1259,8 @@
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1260,31 +1280,34 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E17" s="3">
         <v>35800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>84800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>176800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-18900</v>
-      </c>
       <c r="F18" s="3">
-        <v>-27200</v>
+        <v>-19000</v>
       </c>
       <c r="G18" s="3">
-        <v>-35900</v>
+        <v>-27300</v>
       </c>
       <c r="H18" s="3">
-        <v>-30500</v>
+        <v>-36000</v>
       </c>
       <c r="I18" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-31200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-72700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-169300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,121 +1579,125 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>-23300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>26100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-31200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>53200</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="3">
         <v>-14200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-33300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-42800</v>
+        <v>-18700</v>
       </c>
       <c r="E21" s="3">
-        <v>-32900</v>
+        <v>-19500</v>
       </c>
       <c r="F21" s="3">
-        <v>800</v>
+        <v>-16900</v>
       </c>
       <c r="G21" s="3">
-        <v>-65600</v>
+        <v>-27200</v>
       </c>
       <c r="H21" s="3">
-        <v>-7800</v>
+        <v>-34400</v>
       </c>
       <c r="I21" s="3">
-        <v>23500</v>
+        <v>-28900</v>
       </c>
       <c r="J21" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-85700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-63900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-38600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1700,31 +1737,34 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>42300</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,130 +1817,136 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-44100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-67100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-86900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-67100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-40300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-163900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>16</v>
       </c>
@@ -1916,8 +1962,8 @@
       <c r="V24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-44300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-66900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-87900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-159700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-44000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-66600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-87700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-66900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-159600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>23300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>16000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-26100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>31200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-53200</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="3">
         <v>14200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>33300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-66600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-87700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-66900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-159600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-66600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-87700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-66900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-159600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,118 +3004,122 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>763800</v>
+        <v>213700</v>
       </c>
       <c r="E41" s="3">
-        <v>793000</v>
+        <v>231800</v>
       </c>
       <c r="F41" s="3">
-        <v>851500</v>
+        <v>251900</v>
       </c>
       <c r="G41" s="3">
-        <v>872700</v>
-      </c>
-      <c r="H41" s="3">
-        <v>954400</v>
+        <v>309600</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I41" s="3">
-        <v>986000</v>
+        <v>454600</v>
       </c>
       <c r="J41" s="3">
+        <v>412200</v>
+      </c>
+      <c r="K41" s="3">
         <v>1032000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1020300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1217300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1248000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1291200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1385400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1321800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1395900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>670900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>547100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>532000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>541200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>542000</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>499800</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L42" s="3">
+        <v>573800</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="3">
         <v>20600</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3045,8 +3135,8 @@
       <c r="R42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3072,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3081,153 +3174,159 @@
         <v>17300</v>
       </c>
       <c r="E43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F43" s="3">
         <v>18300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24000</v>
       </c>
-      <c r="G43" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>17900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E44" s="3">
         <v>19300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18400</v>
       </c>
-      <c r="G44" s="3">
-        <v>21300</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3">
         <v>19500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3300</v>
-      </c>
-      <c r="S44" s="3">
-        <v>4000</v>
       </c>
       <c r="T44" s="3">
         <v>4000</v>
       </c>
       <c r="U44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V44" s="3">
         <v>3700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3243,8 +3342,8 @@
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>100</v>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
@@ -3265,13 +3364,13 @@
         <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -3280,11 +3379,11 @@
         <v>100</v>
       </c>
       <c r="T45" s="3">
+        <v>100</v>
+      </c>
+      <c r="U45" s="3">
         <v>9900</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
@@ -3301,141 +3400,147 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>797600</v>
+      </c>
+      <c r="E46" s="3">
         <v>800500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>831000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>894000</v>
       </c>
-      <c r="G46" s="3">
-        <v>909200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>991900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1022300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1064300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1047100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1266400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1276700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1311900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1394300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1330300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1401100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>676100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E47" s="3">
         <v>81300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>112700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>138400</v>
       </c>
-      <c r="G47" s="3">
-        <v>132800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>173000</v>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I47" s="3">
-        <v>161100</v>
+        <v>172200</v>
       </c>
       <c r="J47" s="3">
+        <v>160300</v>
+      </c>
+      <c r="K47" s="3">
         <v>115800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>168100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>63100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>64400</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
-        <v>75100</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
         <v>75100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>75100</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T47" s="3">
         <v>8400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3451,91 +3556,97 @@
       <c r="Y47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E48" s="3">
         <v>26100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28800</v>
       </c>
-      <c r="G48" s="3">
-        <v>27800</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
         <v>28100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>5200</v>
       </c>
       <c r="AA48" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3557,62 +3668,65 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L49" s="3">
         <v>31800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21400</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P49" s="3">
         <v>116800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>118200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3780,37 +3900,37 @@
         <v>900</v>
       </c>
       <c r="G52" s="3">
+        <v>900</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M52" s="3">
         <v>1100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1500</v>
       </c>
       <c r="N52" s="3">
         <v>1500</v>
       </c>
       <c r="O52" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="P52" s="3">
         <v>500</v>
       </c>
       <c r="Q52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
@@ -3834,16 +3954,19 @@
         <v>400</v>
       </c>
       <c r="Y52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z52" s="3">
         <v>300</v>
       </c>
       <c r="AA52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>908100</v>
+      </c>
+      <c r="E54" s="3">
         <v>911000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>974000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1064300</v>
       </c>
-      <c r="G54" s="3">
-        <v>1073100</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>1194200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1210200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1203500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1275900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1342400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1387700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1390000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1523900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1536200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1490400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>689300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>63300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,114 +4184,118 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>23300</v>
+        <v>3400</v>
       </c>
       <c r="E57" s="3">
-        <v>26000</v>
+        <v>2900</v>
       </c>
       <c r="F57" s="3">
-        <v>34400</v>
+        <v>4100</v>
       </c>
       <c r="G57" s="3">
-        <v>36800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>29000</v>
+        <v>4700</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I57" s="3">
-        <v>28700</v>
+        <v>3200</v>
       </c>
       <c r="J57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K57" s="3">
         <v>27900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4500</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>300</v>
       </c>
       <c r="J58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4169,8 +4303,8 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>16</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>16</v>
@@ -4187,8 +4321,8 @@
       <c r="T58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -4208,53 +4342,56 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>16</v>
+      <c r="D59" s="3">
+        <v>20200</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
+        <v>29700</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I59" s="3">
-        <v>5000</v>
+        <v>25800</v>
       </c>
       <c r="J59" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K59" s="3">
         <v>8800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4270,8 +4407,8 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -4285,239 +4422,251 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E60" s="3">
         <v>27000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="K60" s="3">
         <v>37000</v>
       </c>
-      <c r="H60" s="3">
-        <v>29300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>34100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>37000</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E61" s="3">
         <v>8000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9300</v>
       </c>
-      <c r="G61" s="3">
-        <v>9600</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>10800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1400</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>14800</v>
+      </c>
+      <c r="R62" s="3">
+        <v>10300</v>
+      </c>
+      <c r="S62" s="3">
+        <v>12800</v>
+      </c>
+      <c r="T62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W62" s="3">
         <v>4700</v>
       </c>
-      <c r="G62" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>8600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>9300</v>
-      </c>
-      <c r="O62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>14800</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>10300</v>
-      </c>
-      <c r="R62" s="3">
-        <v>12800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>4700</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7400</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>1100</v>
       </c>
       <c r="AA62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>41300</v>
+        <v>40500</v>
       </c>
       <c r="E66" s="3">
-        <v>45600</v>
+        <v>40700</v>
       </c>
       <c r="F66" s="3">
-        <v>49600</v>
+        <v>44700</v>
       </c>
       <c r="G66" s="3">
-        <v>51600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>45500</v>
+        <v>48600</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I66" s="3">
-        <v>50300</v>
+        <v>44600</v>
       </c>
       <c r="J66" s="3">
+        <v>49700</v>
+      </c>
+      <c r="K66" s="3">
         <v>53900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-678300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-670000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-626000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-591200</v>
       </c>
-      <c r="G72" s="3">
-        <v>-590200</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-523600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-514400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-536700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-449000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-382100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-342300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-309200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-149600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-131400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-117800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-108500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-91000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-70300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-62000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-60000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-58600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-54300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-51600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>866600</v>
+      </c>
+      <c r="E76" s="3">
         <v>869600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>928400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1014800</v>
       </c>
-      <c r="G76" s="3">
-        <v>1021500</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>1148700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1159900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1149500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1230700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1291400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1320500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1343400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1494700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1502700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1469700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>667100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>57600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-66600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-87700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-66900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-159600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,44 +6009,45 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="E83" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2000</v>
-      </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H83" s="3">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="I83" s="3">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="J83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5864,8 +6063,8 @@
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,44 +6487,47 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6326,8 +6543,8 @@
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,41 +6599,42 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -6423,8 +6644,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
@@ -6432,8 +6653,8 @@
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,44 +6837,47 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>17200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-139500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>122700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>75600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-225400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>340700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-313800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-53400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-41200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6663,8 +6893,8 @@
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,44 +7267,47 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-53200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-67300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7077,8 +7323,8 @@
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -7101,44 +7347,47 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>3600</v>
-      </c>
       <c r="G101" s="3">
-        <v>-1100</v>
+        <v>2200</v>
       </c>
       <c r="H101" s="3">
-        <v>-1100</v>
+        <v>1000</v>
       </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>-4600</v>
       </c>
       <c r="J101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7154,8 +7403,8 @@
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7178,44 +7427,47 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-57700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-179800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>42400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-273200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>315200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-336000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-81900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-65500</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7231,8 +7483,8 @@
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -7253,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,196 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E8" s="3">
         <v>14900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>800</v>
       </c>
       <c r="R8" s="3">
         <v>800</v>
       </c>
       <c r="S8" s="3">
+        <v>800</v>
+      </c>
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1700</v>
       </c>
       <c r="AA8" s="3">
         <v>1700</v>
@@ -853,168 +856,177 @@
       <c r="AB8" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7200</v>
       </c>
-      <c r="G9" s="3">
-        <v>7400</v>
-      </c>
       <c r="H9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I9" s="3">
         <v>6800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E10" s="3">
         <v>7200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>300</v>
       </c>
       <c r="P10" s="3">
         <v>300</v>
       </c>
       <c r="Q10" s="3">
+        <v>300</v>
+      </c>
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
-      </c>
-      <c r="T10" s="3">
-        <v>-100</v>
       </c>
       <c r="U10" s="3">
         <v>-100</v>
       </c>
       <c r="V10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>9100</v>
       </c>
       <c r="F12" s="3">
         <v>9100</v>
       </c>
       <c r="G12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H12" s="3">
         <v>13600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3700</v>
       </c>
       <c r="S12" s="3">
         <v>3700</v>
       </c>
       <c r="T12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="U12" s="3">
         <v>2600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,13 +1219,16 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>52200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
@@ -1220,8 +1239,8 @@
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
+      <c r="H14" s="3">
+        <v>-25100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
@@ -1229,24 +1248,24 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3">
         <v>40500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
         <v>140300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1262,8 +1281,8 @@
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1283,35 +1302,38 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1363,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E17" s="3">
         <v>35100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32300</v>
       </c>
-      <c r="G17" s="3">
-        <v>41700</v>
-      </c>
       <c r="H17" s="3">
+        <v>43300</v>
+      </c>
+      <c r="I17" s="3">
         <v>48100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>84800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>176800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-27300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-36000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-72700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-169300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,13 +1612,14 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>800</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -1597,8 +1630,8 @@
       <c r="G20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
+      <c r="H20" s="3">
+        <v>-400</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>16</v>
@@ -1606,101 +1639,104 @@
       <c r="J20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3">
         <v>-14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-27200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-34400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-28900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-85700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-63900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-38600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1740,35 +1776,38 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27300</v>
       </c>
-      <c r="G22" s="3">
-        <v>800</v>
-      </c>
       <c r="H22" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I22" s="3">
         <v>42300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1820,8 +1859,11 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1829,127 +1871,130 @@
         <v>-8700</v>
       </c>
       <c r="E23" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-44100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-67100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-86900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-67100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-33700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-163900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>16</v>
       </c>
@@ -1965,8 +2010,8 @@
       <c r="W24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1980,8 +2025,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-44300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-66900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-87900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-159700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-44000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-66600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-87700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-66900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-39700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-33100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-159600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,13 +2606,16 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>-800</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>16</v>
@@ -2557,8 +2626,8 @@
       <c r="G32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
+      <c r="H32" s="3">
+        <v>400</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>16</v>
@@ -2566,142 +2635,148 @@
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="3">
         <v>14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-44000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-66600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-87700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-66900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-33100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-159600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-44000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-66600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-87700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-66900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-33100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-159600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,124 +3090,128 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E41" s="3">
         <v>213700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>231800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>251900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>309600</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="3">
         <v>454600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>412200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1032000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1020300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1217300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1248000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1291200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1385400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1321800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1395900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>670900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>440800</v>
+      </c>
+      <c r="E42" s="3">
         <v>547100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>532000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>541200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>542000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>499800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>573800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="3">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" s="3">
         <v>20600</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3138,8 +3227,8 @@
       <c r="S42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3165,173 +3254,182 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>17300</v>
+        <v>12500</v>
       </c>
       <c r="E43" s="3">
         <v>17300</v>
       </c>
       <c r="F43" s="3">
+        <v>17300</v>
+      </c>
+      <c r="G43" s="3">
         <v>18300</v>
       </c>
-      <c r="G43" s="3">
-        <v>24000</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="H43" s="3">
+        <v>22200</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="3">
         <v>17900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E44" s="3">
         <v>19500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>19700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18400</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3">
         <v>19500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>20000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3300</v>
-      </c>
-      <c r="T44" s="3">
-        <v>4000</v>
       </c>
       <c r="U44" s="3">
         <v>4000</v>
       </c>
       <c r="V44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W44" s="3">
         <v>3700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -3342,11 +3440,11 @@
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -3367,13 +3465,13 @@
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3382,11 +3480,11 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
+        <v>100</v>
+      </c>
+      <c r="V45" s="3">
         <v>9900</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
@@ -3403,147 +3501,153 @@
         <v>0</v>
       </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>789300</v>
+      </c>
+      <c r="E46" s="3">
         <v>797600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>800500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>831000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>894000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="3">
         <v>991900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1022300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1064300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1047100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1266400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1276700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1311900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1394300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1330300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1401100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>676100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>42600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>54500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E47" s="3">
         <v>80600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>81300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>112700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>138400</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3">
         <v>172200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>160300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>115800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>168100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>63100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64400</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
-        <v>75100</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>75100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>75100</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U47" s="3">
         <v>8400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3559,94 +3663,100 @@
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E48" s="3">
         <v>26800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28800</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="3">
         <v>28100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7300</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>5200</v>
       </c>
       <c r="AB48" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3663,7 +3773,7 @@
         <v>2200</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -3671,62 +3781,65 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M49" s="3">
         <v>31800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="3">
         <v>116800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>118200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,13 +4001,16 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>900</v>
@@ -3902,38 +4021,38 @@
       <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>1500</v>
       </c>
       <c r="P52" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="Q52" s="3">
         <v>500</v>
       </c>
       <c r="R52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
@@ -3957,16 +4076,19 @@
         <v>400</v>
       </c>
       <c r="Z52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA52" s="3">
         <v>300</v>
       </c>
       <c r="AB52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>901900</v>
+      </c>
+      <c r="E54" s="3">
         <v>908100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>911000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>974000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1064300</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="3">
         <v>1194200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1210200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1203500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1275900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1342400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1387700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1390000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1523900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1536200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1490400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>689300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>20300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,120 +4314,124 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>23100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>300</v>
       </c>
       <c r="K58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L58" s="3">
         <v>400</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4306,8 +4439,8 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>16</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>16</v>
@@ -4324,8 +4457,8 @@
       <c r="U58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4345,56 +4478,59 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E59" s="3">
         <v>20200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21800</v>
       </c>
-      <c r="G59" s="3">
-        <v>29700</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="H59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="3">
         <v>25800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4410,8 +4546,8 @@
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4425,168 +4561,177 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E60" s="3">
         <v>27800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="3">
         <v>29300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>37000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>10800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1400</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4605,68 +4750,71 @@
       <c r="H62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I62" s="3">
-        <v>100</v>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7400</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>1100</v>
       </c>
       <c r="AB62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E66" s="3">
         <v>40500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48600</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="3">
         <v>44600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-687100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-678300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-670000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-626000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-591200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="3">
         <v>-523600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-514400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-536700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-449000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-382100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-342300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-309200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-149600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-131400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-117800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-108500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-91000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-70300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-62000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-60000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-58600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-53100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-51600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E76" s="3">
         <v>866600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>869600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>928400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1014800</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="3">
         <v>1148700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1159900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1149500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1230700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1291400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1320500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1343400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1494700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1502700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1469700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>667100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>57600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-44000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-66600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-87700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-66900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-33100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-159600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,47 +6207,48 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6066,8 +6264,8 @@
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -6090,8 +6288,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,47 +6703,50 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-29400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6546,8 +6762,8 @@
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -6570,8 +6786,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6609,35 +6829,35 @@
         <v>-500</v>
       </c>
       <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -6647,8 +6867,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
@@ -6656,8 +6876,8 @@
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -6680,8 +6900,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,47 +7066,50 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>9100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>122700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>75600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-225400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>340700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-313800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-53400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6896,8 +7125,8 @@
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -6920,8 +7149,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7209,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,47 +7512,50 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-53200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-67300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7326,8 +7571,8 @@
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -7350,47 +7595,50 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1100</v>
+        <v>3600</v>
       </c>
       <c r="E101" s="3">
         <v>-1100</v>
       </c>
       <c r="F101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7406,8 +7654,8 @@
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -7430,47 +7678,50 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-57700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-179800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>42400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-273200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>315200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-336000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-81900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-65500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7486,8 +7737,8 @@
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -7508,6 +7759,9 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,202 +656,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
         <v>14600</v>
       </c>
-      <c r="E8" s="3">
-        <v>14900</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3">
         <v>15000</v>
       </c>
-      <c r="G8" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
         <v>14500</v>
       </c>
-      <c r="I8" s="3">
-        <v>12200</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3">
         <v>14700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1300</v>
-      </c>
-      <c r="R8" s="3">
-        <v>800</v>
       </c>
       <c r="S8" s="3">
         <v>800</v>
       </c>
       <c r="T8" s="3">
+        <v>800</v>
+      </c>
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1700</v>
       </c>
       <c r="AB8" s="3">
         <v>1700</v>
@@ -859,174 +863,183 @@
       <c r="AC8" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
         <v>8100</v>
       </c>
-      <c r="E9" s="3">
-        <v>7700</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3">
         <v>8200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="M9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="O9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="Q9" s="3">
         <v>7200</v>
       </c>
-      <c r="H9" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J9" s="3">
-        <v>8200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>8400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>4400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>8200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>7500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>9400</v>
-      </c>
-      <c r="P9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3">
         <v>6800</v>
       </c>
-      <c r="G10" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
         <v>7100</v>
       </c>
-      <c r="I10" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="3">
         <v>6500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>300</v>
       </c>
       <c r="Q10" s="3">
         <v>300</v>
       </c>
       <c r="R10" s="3">
+        <v>300</v>
+      </c>
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>-100</v>
       </c>
       <c r="V10" s="3">
         <v>-100</v>
       </c>
       <c r="W10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
         <v>9100</v>
       </c>
-      <c r="E12" s="3">
-        <v>9800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>9100</v>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G12" s="3">
         <v>9100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3">
         <v>13600</v>
       </c>
-      <c r="I12" s="3">
-        <v>12800</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3">
         <v>16400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>3700</v>
       </c>
       <c r="T12" s="3">
         <v>3700</v>
       </c>
       <c r="U12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="V12" s="3">
         <v>2600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,53 +1239,56 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>52200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
         <v>-25100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>40500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="3">
         <v>140300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1284,8 +1304,8 @@
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1305,38 +1325,41 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>1700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
         <v>40000</v>
       </c>
-      <c r="E17" s="3">
-        <v>35100</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3">
         <v>35800</v>
       </c>
-      <c r="G17" s="3">
-        <v>32300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
         <v>43300</v>
       </c>
-      <c r="I17" s="3">
-        <v>48100</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="3">
         <v>45200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>84800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>176800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25400</v>
       </c>
-      <c r="E18" s="3">
-        <v>-20300</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3">
         <v>-20800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
         <v>-28900</v>
       </c>
-      <c r="I18" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="3">
         <v>-30400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-72700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-169300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1613,133 +1646,137 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-33300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24600</v>
       </c>
-      <c r="E21" s="3">
-        <v>-18700</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-19500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-16900</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-28400</v>
       </c>
-      <c r="I21" s="3">
-        <v>-34400</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-28900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-85700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-63900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-38600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-32600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1779,38 +1816,41 @@
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3">
         <v>-60500</v>
       </c>
-      <c r="E22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3">
         <v>33800</v>
       </c>
-      <c r="G22" s="3">
-        <v>27300</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3">
         <v>-7900</v>
       </c>
-      <c r="I22" s="3">
-        <v>42300</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1862,142 +1902,148 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-8700</v>
+      <c r="D23" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E23" s="3">
         <v>-8700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="3">
         <v>-44100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-67100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="O23" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-163900</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="T23" s="3">
         <v>-9300</v>
       </c>
-      <c r="K23" s="3">
-        <v>22000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-86900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-67100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-40300</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-163900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
+      <c r="J24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>16</v>
       </c>
@@ -2013,8 +2059,8 @@
       <c r="X24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2028,8 +2074,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9100</v>
       </c>
-      <c r="E26" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3">
         <v>-44300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
-        <v>-66900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="3">
         <v>-9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-87900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-67100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>22200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-87700</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="F27" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-66600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>22200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-87700</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-66900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-159600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-17400</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-20700</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3">
         <v>14200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>33300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>22200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-87700</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="F33" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-66600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>22200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-87700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-66900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-159600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-17400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-20700</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>22200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-87700</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="F35" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-66600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>22200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-87700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-66900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-159600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-17400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-20700</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,130 +3177,134 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3">
         <v>317200</v>
       </c>
-      <c r="E41" s="3">
-        <v>213700</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="3">
         <v>231800</v>
       </c>
-      <c r="G41" s="3">
-        <v>251900</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
         <v>309600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="3">
         <v>454600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>412200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1032000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1020300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1217300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1248000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1291200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1385400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1321800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1395900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>670900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>440800</v>
       </c>
-      <c r="E42" s="3">
-        <v>547100</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>532000</v>
       </c>
-      <c r="G42" s="3">
-        <v>541200</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>542000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>499800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>573800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O42" s="3">
         <v>20600</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3230,8 +3320,8 @@
       <c r="T42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3257,197 +3347,206 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3">
         <v>12500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="3">
         <v>17300</v>
       </c>
-      <c r="F43" s="3">
-        <v>17300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>18300</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>22200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" s="3">
         <v>17900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3">
         <v>16900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3">
+        <v>19300</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3">
+        <v>18400</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" s="3">
         <v>19500</v>
       </c>
-      <c r="F44" s="3">
-        <v>19300</v>
-      </c>
-      <c r="G44" s="3">
-        <v>19700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>18400</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="3">
-        <v>19500</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3300</v>
-      </c>
-      <c r="U44" s="3">
-        <v>4000</v>
       </c>
       <c r="V44" s="3">
         <v>4000</v>
       </c>
       <c r="W44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X44" s="3">
         <v>3700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -3468,13 +3567,13 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
@@ -3483,11 +3582,11 @@
         <v>100</v>
       </c>
       <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3">
         <v>9900</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
@@ -3504,153 +3603,159 @@
         <v>0</v>
       </c>
       <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3">
         <v>789300</v>
       </c>
-      <c r="E46" s="3">
-        <v>797600</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="3">
         <v>800500</v>
       </c>
-      <c r="G46" s="3">
-        <v>831000</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>894000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46" s="3">
         <v>991900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1022300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1064300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1047100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1266400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1276700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1311900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1394300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1330300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1401100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>676100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>42600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>54500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3">
         <v>86200</v>
       </c>
-      <c r="E47" s="3">
-        <v>80600</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3">
         <v>81300</v>
       </c>
-      <c r="G47" s="3">
-        <v>112700</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3">
         <v>138400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" s="3">
         <v>172200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>160300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>115800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>168100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>63100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>64400</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
-        <v>75100</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>75100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>75100</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V47" s="3">
         <v>8400</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3666,180 +3771,189 @@
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3">
         <v>23500</v>
       </c>
-      <c r="E48" s="3">
-        <v>26800</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="3">
         <v>26100</v>
       </c>
-      <c r="G48" s="3">
-        <v>27200</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
         <v>28800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="3">
         <v>28100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>5200</v>
       </c>
       <c r="AC48" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>2200</v>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E49" s="3">
         <v>2200</v>
       </c>
-      <c r="F49" s="3">
-        <v>2200</v>
+      <c r="F49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G49" s="3">
         <v>2200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N49" s="3">
         <v>31800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>21400</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R49" s="3">
         <v>116800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>118200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,58 +4121,61 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
-        <v>900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>900</v>
+      <c r="F52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52" s="3">
         <v>1700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1500</v>
       </c>
       <c r="P52" s="3">
         <v>1500</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="R52" s="3">
         <v>500</v>
       </c>
       <c r="S52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
@@ -4079,16 +4199,19 @@
         <v>400</v>
       </c>
       <c r="AA52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AB52" s="3">
         <v>300</v>
       </c>
       <c r="AC52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3">
         <v>901900</v>
       </c>
-      <c r="E54" s="3">
-        <v>908100</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="3">
         <v>911000</v>
       </c>
-      <c r="G54" s="3">
-        <v>974000</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>1064300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" s="3">
         <v>1194200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1210200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1203500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1275900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1342400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1387700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1523900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1536200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1490400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>689300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>63300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,126 +4445,130 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>21800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>23100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3">
         <v>4100</v>
       </c>
-      <c r="E58" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="3">
         <v>4500</v>
       </c>
-      <c r="H58" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
+      <c r="J58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
       </c>
       <c r="L58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M58" s="3">
         <v>400</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4442,8 +4576,8 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>16</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>16</v>
@@ -4460,8 +4594,8 @@
       <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4481,59 +4615,62 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3">
         <v>3700</v>
       </c>
-      <c r="E59" s="3">
-        <v>20200</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3">
         <v>20400</v>
       </c>
-      <c r="G59" s="3">
-        <v>21800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59" s="3">
         <v>25800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4549,8 +4686,8 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4564,174 +4701,183 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3">
         <v>30800</v>
       </c>
-      <c r="E60" s="3">
-        <v>27800</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="3">
         <v>27000</v>
       </c>
-      <c r="G60" s="3">
-        <v>30400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
         <v>34500</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="3">
         <v>29300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>37000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>6800</v>
       </c>
-      <c r="E61" s="3">
-        <v>7800</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>8000</v>
       </c>
-      <c r="G61" s="3">
-        <v>8300</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>9300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>10800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4753,68 +4899,71 @@
       <c r="I62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J62" s="3">
-        <v>100</v>
+      <c r="J62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
       </c>
       <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7400</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>1100</v>
       </c>
       <c r="AC62" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3">
         <v>43200</v>
       </c>
-      <c r="E66" s="3">
-        <v>40500</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="3">
         <v>40700</v>
       </c>
-      <c r="G66" s="3">
-        <v>44700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="3">
         <v>48600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="3">
         <v>44600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
         <v>-687100</v>
       </c>
-      <c r="E72" s="3">
-        <v>-678300</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="3">
         <v>-670000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-626000</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-591200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="3">
         <v>-523600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-514400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-536700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-449000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-382100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-342300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-309200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-149600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-131400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-117800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-108500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-91000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-70300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-62000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-58600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-54300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-53100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-51600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3">
         <v>858000</v>
       </c>
-      <c r="E76" s="3">
-        <v>866600</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="3">
         <v>869600</v>
       </c>
-      <c r="G76" s="3">
-        <v>928400</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>1014800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="3">
         <v>1148700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1159900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1149500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1230700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1291400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1320500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1343400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1494700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1502700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1469700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>667100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>57600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>22200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-87700</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="F81" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-66600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>22200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-87700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-66900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-159600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-17400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-20700</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,50 +6406,51 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6267,8 +6466,8 @@
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,50 +6920,53 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3">
         <v>-17700</v>
       </c>
-      <c r="G89" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3">
         <v>-29400</v>
       </c>
-      <c r="I89" s="3">
-        <v>-19500</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K89" s="3">
         <v>-28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6765,8 +6982,8 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -6789,8 +7006,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,47 +7040,48 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-500</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I91" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -6870,8 +7091,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
@@ -6879,8 +7100,8 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,50 +7296,53 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3">
         <v>117200</v>
       </c>
-      <c r="E94" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3">
         <v>17200</v>
       </c>
-      <c r="G94" s="3">
-        <v>9100</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3">
         <v>-139500</v>
       </c>
-      <c r="I94" s="3">
-        <v>122700</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="3">
         <v>75600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-225400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>340700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-313800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-53400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7128,8 +7358,8 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7212,8 +7446,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,50 +7758,53 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3">
         <v>-19500</v>
       </c>
-      <c r="G100" s="3">
-        <v>-53200</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3">
         <v>-14400</v>
       </c>
-      <c r="I100" s="3">
-        <v>-67300</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7574,8 +7820,8 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -7598,50 +7844,53 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3">
         <v>3600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="O101" s="3">
         <v>-4600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="P101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7657,8 +7906,8 @@
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7681,50 +7930,53 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>103500</v>
       </c>
-      <c r="E102" s="3">
-        <v>-18100</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-20100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-57700</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-179800</v>
       </c>
-      <c r="I102" s="3">
-        <v>34800</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>42400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-273200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>315200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-336000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-81900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-65500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7740,8 +7992,8 @@
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -7762,6 +8014,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NNDM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>NNDM</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -664,382 +664,421 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>16</v>
+      <c r="D8" s="3">
+        <v>29700</v>
       </c>
       <c r="E8" s="3">
+        <v>31100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>31100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H8" s="3">
         <v>14600</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>15000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14500</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="3">
+        <v>14500</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="3">
         <v>14700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>15000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>10000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>11100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>7500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>1300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>2000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>2000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>2200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>2900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>1700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>1700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
+      <c r="D9" s="3">
+        <v>17600</v>
       </c>
       <c r="E9" s="3">
-        <v>8100</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
+        <v>20400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>20400</v>
       </c>
       <c r="G9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I9" s="3">
         <v>8200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="3">
         <v>7300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="3">
-        <v>8200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>8400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>4400</v>
+      <c r="M9" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N9" s="3">
         <v>8200</v>
       </c>
       <c r="O9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="P9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>9400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>7200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>1000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Y9" s="3">
         <v>500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA9" s="3">
         <v>600</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>2300</v>
       </c>
       <c r="AB9" s="3">
         <v>1300</v>
       </c>
       <c r="AC9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF9" s="3">
         <v>1600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>16</v>
+      <c r="D10" s="3">
+        <v>12100</v>
       </c>
       <c r="E10" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="3">
         <v>6500</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>6600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>7700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>3600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>300</v>
-      </c>
-      <c r="R10" s="3">
-        <v>300</v>
-      </c>
-      <c r="S10" s="3">
-        <v>200</v>
       </c>
       <c r="T10" s="3">
         <v>300</v>
       </c>
       <c r="U10" s="3">
+        <v>300</v>
+      </c>
+      <c r="V10" s="3">
+        <v>200</v>
+      </c>
+      <c r="W10" s="3">
+        <v>300</v>
+      </c>
+      <c r="X10" s="3">
         <v>1100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>-100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1109,106 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>16</v>
+      <c r="D12" s="3">
+        <v>8200</v>
       </c>
       <c r="E12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="I12" s="3">
         <v>9100</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
+        <v>16700</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="3">
+        <v>13600</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="3">
+        <v>16400</v>
+      </c>
+      <c r="O12" s="3">
+        <v>19300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>18500</v>
+      </c>
+      <c r="R12" s="3">
+        <v>18400</v>
+      </c>
+      <c r="S12" s="3">
+        <v>17900</v>
+      </c>
+      <c r="T12" s="3">
+        <v>15100</v>
+      </c>
+      <c r="U12" s="3">
+        <v>13700</v>
+      </c>
+      <c r="V12" s="3">
         <v>9100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="3">
-        <v>16400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>19300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>21000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>18500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>18400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>17900</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>15100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>13700</v>
-      </c>
-      <c r="S12" s="3">
-        <v>9100</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <v>3700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Y12" s="3">
         <v>2600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Z12" s="3">
         <v>1900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AA12" s="3">
         <v>1700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AB12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AC12" s="3">
         <v>2100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AD12" s="3">
         <v>4500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AE12" s="3">
         <v>2200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AF12" s="3">
         <v>1800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AG12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,62 +1293,71 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>52000</v>
       </c>
       <c r="E14" s="3">
-        <v>52200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>26100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>21800</v>
+      </c>
+      <c r="H14" s="3">
+        <v>53200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>-25100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
         <v>40500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="3">
         <v>140300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1307,14 +1367,14 @@
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1328,47 +1388,56 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E15" s="3">
-        <v>1700</v>
+        <v>6100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="G15" s="3">
+        <v>600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>700</v>
+      </c>
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="O15" s="3">
         <v>1400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1414,8 +1483,17 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1521,201 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>16</v>
+      <c r="D17" s="3">
+        <v>50700</v>
       </c>
       <c r="E17" s="3">
-        <v>40000</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>16</v>
+        <v>46900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46900</v>
       </c>
       <c r="G17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I17" s="3">
         <v>35800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>46200</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="3">
         <v>43300</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="3">
         <v>45200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>46200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>84800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>43800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>43200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>43300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>176800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>25800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>20700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>10400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>10500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>20300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>4100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>4200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>5100</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>5500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>6600</v>
       </c>
       <c r="AC17" s="3">
         <v>5500</v>
       </c>
       <c r="AD17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AG17" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>16</v>
+      <c r="D18" s="3">
+        <v>-21000</v>
       </c>
       <c r="E18" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>16</v>
+        <v>-15800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-15800</v>
       </c>
       <c r="G18" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-20800</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="3">
         <v>-28900</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="3">
         <v>-30400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-31200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-72700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-33800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>-32100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>-169300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>-24500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-19900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-8500</v>
       </c>
       <c r="V18" s="3">
         <v>-19900</v>
       </c>
       <c r="W18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AE18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1647,145 +1746,157 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>-3500</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="3">
         <v>-14200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>-33300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>-8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>5400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>5800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>-8900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>-4500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AD20" s="3">
         <v>5700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AE20" s="3">
         <v>3400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-13800</v>
       </c>
       <c r="E21" s="3">
-        <v>-24600</v>
+        <v>-9900</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-9900</v>
       </c>
       <c r="G21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-19500</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-28400</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-28900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>-29800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>-85700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>-63900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>-38600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1819,47 +1930,56 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
+      <c r="D22" s="3">
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>-60500</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="I22" s="3">
         <v>33800</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="3">
         <v>-7900</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="O22" s="3">
         <v>3600</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1905,94 +2025,112 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>16</v>
+      <c r="D23" s="3">
+        <v>-69700</v>
       </c>
       <c r="E23" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>16</v>
+        <v>-35400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-35400</v>
       </c>
       <c r="G23" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-44100</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N23" s="3">
         <v>-9300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>22000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-86900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-67100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>-40300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>-163900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-18800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-13800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>-9300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>-17400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>-20700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>-8300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AA23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AB23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AG23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2000,59 +2138,59 @@
         <v>16</v>
       </c>
       <c r="E24" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="T24" s="3">
         <v>-4300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>16</v>
       </c>
@@ -2062,14 +2200,14 @@
       <c r="Y24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2077,8 +2215,17 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2310,207 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>16</v>
+      <c r="D26" s="3">
+        <v>-69700</v>
       </c>
       <c r="E26" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>16</v>
+        <v>-31700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-31700</v>
       </c>
       <c r="G26" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-44300</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="3">
         <v>-9400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>22000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-87900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-67100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>-40000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>-159700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-18300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-13600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>-9300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>-17400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>-20700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AA26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AE26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AF26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AG26" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>16</v>
+      <c r="D27" s="3">
+        <v>-69700</v>
       </c>
       <c r="E27" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>16</v>
+        <v>-43500</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-43500</v>
       </c>
       <c r="G27" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-44000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>22200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>-87700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>-66900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>-39700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>-159600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>-18200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-13600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-9300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>-17400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>-20700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AA27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AE27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AF27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AG27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2595,17 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2430,10 +2613,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -2507,8 +2690,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2785,17 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2880,207 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>3500</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P32" s="3">
         <v>14200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>33300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>-5400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>-5800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>8900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Z32" s="3">
         <v>4500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AD32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AE32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>16</v>
+      <c r="D33" s="3">
+        <v>-69700</v>
       </c>
       <c r="E33" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>16</v>
+        <v>-43500</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-43500</v>
       </c>
       <c r="G33" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-44000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>22200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-87700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>-66900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>-39700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>-159600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-18200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-13600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>-9300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>-17400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>-20700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AA33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AE33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AF33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AG33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3165,212 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>16</v>
+      <c r="D35" s="3">
+        <v>-69700</v>
       </c>
       <c r="E35" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>16</v>
+        <v>-43500</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-43500</v>
       </c>
       <c r="G35" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-44000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>22200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-87700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>-66900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>-39700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>-159600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-18200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-13600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>-9300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>-17400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>-20700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AA35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AE35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AF35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AG35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3401,11 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,142 +3436,154 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>16</v>
+      <c r="D41" s="3">
+        <v>355300</v>
       </c>
       <c r="E41" s="3">
+        <v>204700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>204700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>487400</v>
+      </c>
+      <c r="H41" s="3">
         <v>317200</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>231800</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>309600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="3">
+        <v>309600</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N41" s="3">
         <v>454600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>412200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>1032000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>1020300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>1217300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>1248000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>1291200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>1385400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>1321800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>1395900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>670900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>37300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>39700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>4500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>3900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AC41" s="3">
         <v>5500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AD41" s="3">
         <v>5300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AE41" s="3">
         <v>10200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AF41" s="3">
         <v>3800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AG41" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>84500</v>
       </c>
       <c r="E42" s="3">
+        <v>253200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>253200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>257200</v>
+      </c>
+      <c r="H42" s="3">
         <v>440800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>532000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>542000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>542000</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>499800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>573800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R42" s="3">
         <v>20600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3323,14 +3593,14 @@
       <c r="U42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3350,212 +3620,239 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>16</v>
+      <c r="D43" s="3">
+        <v>22700</v>
       </c>
       <c r="E43" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>26000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>17400</v>
+      </c>
+      <c r="H43" s="3">
         <v>12500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>17300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22200</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43" s="3">
+        <v>22200</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" s="3">
         <v>17900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>16200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>12800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>8900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>12500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>13500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>9300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>4700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>4200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>2000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>1200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AA43" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>2800</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>1700</v>
       </c>
       <c r="AB43" s="3">
         <v>2400</v>
       </c>
       <c r="AC43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF43" s="3">
         <v>1900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AG43" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>16</v>
+      <c r="D44" s="3">
+        <v>31700</v>
       </c>
       <c r="E44" s="3">
+        <v>32900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>32900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>16800</v>
+      </c>
+      <c r="H44" s="3">
         <v>16900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>19300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18400</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="3">
+        <v>18400</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="3">
         <v>19500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>20000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>19400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>17800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>16000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>15100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>11200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>4000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>4100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>3200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>3300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>4000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>4000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AA44" s="3">
         <v>3700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AB44" s="3">
         <v>3500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AC44" s="3">
         <v>3600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AD44" s="3">
         <v>4000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AE44" s="3">
         <v>3300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AF44" s="3">
         <v>3100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AG44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>16</v>
+      <c r="D45" s="3">
+        <v>11200</v>
       </c>
       <c r="E45" s="3">
-        <v>500</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>4700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4700</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
+      <c r="H45" s="3">
+        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
-        <v>100</v>
+      <c r="M45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -3570,32 +3867,32 @@
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
       <c r="U45" s="3">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3">
+        <v>200</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>9900</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
@@ -3606,165 +3903,183 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>16</v>
+      <c r="D46" s="3">
+        <v>505400</v>
       </c>
       <c r="E46" s="3">
+        <v>525800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>525800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>778900</v>
+      </c>
+      <c r="H46" s="3">
         <v>789300</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>800500</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>894000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="3">
+        <v>894000</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N46" s="3">
         <v>991900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>1022300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>1064300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>1047100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>1266400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>1276700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>1311900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>1394300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>1330300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>1401100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>676100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>42600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>54500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AA46" s="3">
         <v>10300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AB46" s="3">
         <v>9900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AC46" s="3">
         <v>11900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AD46" s="3">
         <v>11000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AE46" s="3">
         <v>15900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AF46" s="3">
         <v>8800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AG46" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3">
+        <v>94900</v>
+      </c>
+      <c r="H47" s="3">
         <v>86200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>81300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>138400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="3">
+        <v>138400</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N47" s="3">
         <v>172200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>160300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>115800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>168100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>28700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="S47" s="3">
         <v>63100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="T47" s="3">
         <v>64400</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>75100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="W47" s="3">
         <v>75100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y47" s="3">
         <v>8400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3774,186 +4089,213 @@
       <c r="AB47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>16</v>
+      <c r="D48" s="3">
+        <v>46100</v>
       </c>
       <c r="E48" s="3">
-        <v>23500</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>48600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>48600</v>
       </c>
       <c r="G48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="I48" s="3">
         <v>26100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" s="3">
         <v>28800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N48" s="3">
         <v>28100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>25500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>22400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>27100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>25800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>25000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>12400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>12000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>9500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>8300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>7200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>6600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AA48" s="3">
         <v>7100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>7400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AC48" s="3">
         <v>9000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AD48" s="3">
         <v>7000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AE48" s="3">
         <v>7300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AF48" s="3">
         <v>5200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AG48" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>16</v>
+      <c r="D49" s="3">
+        <v>18300</v>
       </c>
       <c r="E49" s="3">
+        <v>59800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>59800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H49" s="3">
         <v>2200</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="J49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="3">
         <v>31800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>20400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>21400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U49" s="3">
         <v>116800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="V49" s="3">
         <v>118200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="W49" s="3">
         <v>4200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="X49" s="3">
         <v>4400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Y49" s="3">
         <v>4600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Z49" s="3">
         <v>4800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AA49" s="3">
         <v>5000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AB49" s="3">
         <v>5200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AC49" s="3">
         <v>5400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AD49" s="3">
         <v>5600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AE49" s="3">
         <v>5800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AF49" s="3">
         <v>6000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AG49" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4380,17 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,67 +4475,76 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>16</v>
+      <c r="D52" s="3">
+        <v>3000</v>
       </c>
       <c r="E52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="3">
-        <v>900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>16</v>
+      <c r="H52" s="3">
+        <v>800</v>
       </c>
       <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>400</v>
-      </c>
-      <c r="U52" s="3">
-        <v>400</v>
-      </c>
-      <c r="V52" s="3">
-        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>400</v>
@@ -4202,16 +4562,25 @@
         <v>400</v>
       </c>
       <c r="AB52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AD52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4665,112 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>16</v>
+      <c r="D54" s="3">
+        <v>573200</v>
       </c>
       <c r="E54" s="3">
-        <v>901900</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>16</v>
+        <v>638200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>638200</v>
       </c>
       <c r="G54" s="3">
+        <v>898200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>902500</v>
+      </c>
+      <c r="I54" s="3">
         <v>911000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>1064600</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L54" s="3">
         <v>1064300</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N54" s="3">
         <v>1194200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>1210200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>1203500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>1275900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>1342400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>1387700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>1390000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>1523900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>1536200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>1490400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>689300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>63300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>66400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AA54" s="3">
         <v>22800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AB54" s="3">
         <v>22900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AC54" s="3">
         <v>26700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AD54" s="3">
         <v>24000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AE54" s="3">
         <v>29300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AF54" s="3">
         <v>20300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AG54" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4801,11 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,147 +4836,159 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>16</v>
+      <c r="D57" s="3">
+        <v>13000</v>
       </c>
       <c r="E57" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>27900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>21800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>24600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>23100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>16700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>9800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="V57" s="3">
         <v>8500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="W57" s="3">
         <v>7100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="X57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Z57" s="3">
         <v>4300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AA57" s="3">
         <v>4200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>3900</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>4000</v>
       </c>
       <c r="AB57" s="3">
         <v>4400</v>
       </c>
       <c r="AC57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AF57" s="3">
         <v>3600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AG57" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>16</v>
+      <c r="D58" s="3">
+        <v>8800</v>
       </c>
       <c r="E58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G58" s="3">
         <v>4100</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="3">
         <v>4500</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>16</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>16</v>
@@ -4597,14 +4999,14 @@
       <c r="W58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4618,68 +5020,77 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>16</v>
+      <c r="D59" s="3">
+        <v>13300</v>
       </c>
       <c r="E59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>16</v>
+        <v>16000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>16000</v>
       </c>
       <c r="G59" s="3">
+        <v>18800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I59" s="3">
         <v>20400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" s="3">
         <v>25800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>28200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>8800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>9900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>20400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>15300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>6300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4689,14 +5100,14 @@
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -4704,191 +5115,218 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>16</v>
+      <c r="D60" s="3">
+        <v>56100</v>
       </c>
       <c r="E60" s="3">
-        <v>30800</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>16</v>
+        <v>52500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>52500</v>
       </c>
       <c r="G60" s="3">
+        <v>53500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>30100</v>
+      </c>
+      <c r="I60" s="3">
         <v>27000</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>33000</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L60" s="3">
         <v>34500</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N60" s="3">
         <v>29300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>34100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>37000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>30300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>34500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>43500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>32000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>14500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="V60" s="3">
         <v>14800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>7100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="X60" s="3">
         <v>6700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Y60" s="3">
         <v>5300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>4300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AA60" s="3">
         <v>4200</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>3900</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>4000</v>
       </c>
       <c r="AB60" s="3">
         <v>4400</v>
       </c>
       <c r="AC60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AF60" s="3">
         <v>3600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AG60" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="E61" s="3">
-        <v>6800</v>
+        <v>23500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="G61" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I61" s="3">
         <v>8000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>9300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>10800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>12100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>13100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>11300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>11900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="S61" s="3">
         <v>14200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>4400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>3600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="V61" s="3">
         <v>3900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="W61" s="3">
         <v>3300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="X61" s="3">
         <v>2600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Y61" s="3">
         <v>1800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Z61" s="3">
         <v>1700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AA61" s="3">
         <v>1800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AB61" s="3">
         <v>2100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AC61" s="3">
         <v>3500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AD61" s="3">
         <v>1300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AE61" s="3">
         <v>1400</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
+      <c r="D62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>3000</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>16</v>
@@ -4902,68 +5340,77 @@
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>3000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>8600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>9300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="U62" s="3">
         <v>10600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="V62" s="3">
         <v>14800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="W62" s="3">
         <v>10300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>12800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>3500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AA62" s="3">
         <v>1400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AB62" s="3">
         <v>4700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AC62" s="3">
         <v>8400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AD62" s="3">
         <v>3700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AE62" s="3">
         <v>7400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5495,17 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5590,17 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5685,112 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>16</v>
+      <c r="D66" s="3">
+        <v>87800</v>
       </c>
       <c r="E66" s="3">
-        <v>43200</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>16</v>
+        <v>86200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>86200</v>
       </c>
       <c r="G66" s="3">
+        <v>65300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>41800</v>
+      </c>
+      <c r="I66" s="3">
         <v>40700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
+        <v>45700</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L66" s="3">
         <v>48600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66" s="3">
         <v>44600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>49700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>53900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>45200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>51000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>67200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>46600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>29300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>33400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>20700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>22100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>10600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>8800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>7400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>11300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3">
         <v>15800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AD66" s="3">
         <v>8900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AE66" s="3">
         <v>13200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AF66" s="3">
         <v>4700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AG66" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5821,11 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5910,17 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +6005,17 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +6100,17 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +6195,112 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>16</v>
+      <c r="D72" s="3">
+        <v>-1040600</v>
       </c>
       <c r="E72" s="3">
-        <v>-687100</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>16</v>
+        <v>-971000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-971000</v>
       </c>
       <c r="G72" s="3">
+        <v>-710900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-679800</v>
+      </c>
+      <c r="I72" s="3">
         <v>-670000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>-578200</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="3">
         <v>-591200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" s="3">
         <v>-523600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-514400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-536700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-449000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-382100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-342300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-309200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-149600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-131400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>-117800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>-108500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-91000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-70300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AA72" s="3">
         <v>-62000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AB72" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AC72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AD72" s="3">
         <v>-54300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AE72" s="3">
         <v>-53100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AF72" s="3">
         <v>-51600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AG72" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6385,17 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6480,17 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6575,112 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>16</v>
+      <c r="D76" s="3">
+        <v>485400</v>
       </c>
       <c r="E76" s="3">
-        <v>858000</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>16</v>
+        <v>552000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>552000</v>
       </c>
       <c r="G76" s="3">
+        <v>832400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>860000</v>
+      </c>
+      <c r="I76" s="3">
         <v>869600</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
+        <v>1017900</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" s="3">
         <v>1014800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N76" s="3">
         <v>1148700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>1159900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>1149500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>1230700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>1291400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>1320500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>1343400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>1494700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>1502700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>1469700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>667100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>52700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>57600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>15300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>11600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AC76" s="3">
         <v>10900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AD76" s="3">
         <v>15100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AE76" s="3">
         <v>16100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AF76" s="3">
         <v>15600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AG76" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6765,212 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>16</v>
+      <c r="D81" s="3">
+        <v>-69700</v>
       </c>
       <c r="E81" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>16</v>
+        <v>-43500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-43500</v>
       </c>
       <c r="G81" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-44000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>22200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-87700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>-66900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>-39700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>-159600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-18200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-13600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>-9300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>-17400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>-20700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AA81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AE81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AF81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AG81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,59 +7001,62 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>16</v>
+      <c r="D83" s="3">
+        <v>-2300</v>
       </c>
       <c r="E83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>16</v>
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
+        <v>-2600</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>16</v>
+      <c r="H83" s="3">
+        <v>1200</v>
       </c>
       <c r="I83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6469,14 +7066,14 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6493,8 +7090,17 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +7185,17 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +7280,17 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +7375,17 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7470,17 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,59 +7565,68 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>16</v>
+      <c r="D89" s="3">
+        <v>-7100</v>
       </c>
       <c r="E89" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>16</v>
+        <v>-17500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-17500</v>
       </c>
       <c r="G89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H89" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I89" s="3">
         <v>-17700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="3">
         <v>-29400</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" s="3">
         <v>-28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-28000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-26400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-22300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>-21900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6985,14 +7636,14 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -7009,8 +7660,17 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,76 +7701,79 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>16</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7127,8 +7790,17 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7885,17 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,59 +7980,68 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>16</v>
+      <c r="D94" s="3">
+        <v>157500</v>
       </c>
       <c r="E94" s="3">
-        <v>117200</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>16</v>
+        <v>39600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>39600</v>
       </c>
       <c r="G94" s="3">
+        <v>177100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>74400</v>
+      </c>
+      <c r="I94" s="3">
         <v>17200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="3">
         <v>-139500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" s="3">
         <v>75600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-225400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>340700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-313800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-53400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7361,14 +8051,14 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -7385,8 +8075,17 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +8116,11 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7449,14 +8151,14 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7503,8 +8205,17 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +8300,17 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +8395,17 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,59 +8490,68 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>16</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>16</v>
+        <v>-12500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-12500</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I100" s="3">
         <v>-19500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="3">
         <v>-14400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-19800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7823,14 +8561,14 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7847,59 +8585,68 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>16</v>
+      <c r="D101" s="3">
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>3600</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>16</v>
+      <c r="H101" s="3">
+        <v>2200</v>
       </c>
       <c r="I101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3">
         <v>-4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>-4600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="S101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7909,14 +8656,14 @@
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7933,59 +8680,68 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>150700</v>
       </c>
       <c r="E102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>169800</v>
+      </c>
+      <c r="H102" s="3">
         <v>103500</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-20100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-179800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-179800</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>42400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-273200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>315200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-336000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-81900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>-65500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7995,14 +8751,14 @@
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -8017,6 +8773,15 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
